--- a/output/pdf_financials_xlsx/FDY.xlsx
+++ b/output/pdf_financials_xlsx/FDY.xlsx
@@ -1117,19 +1117,19 @@
         <v>-1.059681</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>5.476554</v>
+        <v>-5.476554</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>8.076884</v>
+        <v>-8.076884</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>20.499964</v>
+        <v>-20.499964</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>22.548709</v>
+        <v>-22.548709</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>27.868658</v>
+        <v>-27.868658</v>
       </c>
     </row>
     <row r="17">
@@ -1353,19 +1353,19 @@
         <v>-1.059681</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>5.476554</v>
+        <v>-5.476554</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>8.076884</v>
+        <v>-8.076884</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>20.499964</v>
+        <v>-20.499964</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>22.548709</v>
+        <v>-22.548709</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>27.868658</v>
+        <v>-27.868658</v>
       </c>
     </row>
     <row r="21">
@@ -1491,19 +1491,19 @@
         <v>-1.059681</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>5.476554</v>
+        <v>-5.476554</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>8.076884</v>
+        <v>-8.076884</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>20.499964</v>
+        <v>-20.499964</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>22.548709</v>
+        <v>-22.548709</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>27.868658</v>
+        <v>-27.868658</v>
       </c>
     </row>
     <row r="24">
@@ -1637,19 +1637,19 @@
         </is>
       </c>
       <c r="J26" s="3" t="n">
-        <v>91.27589999999999</v>
+        <v>-91.27589999999999</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>115.384057</v>
+        <v>-115.384057</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>170.833033</v>
+        <v>-170.833033</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>187.905908</v>
+        <v>-187.905908</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>232.238817</v>
+        <v>-232.238817</v>
       </c>
     </row>
     <row r="27">
@@ -1683,19 +1683,19 @@
         <v>-1.059681</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>5.476554</v>
+        <v>-5.476554</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>8.076884</v>
+        <v>-8.076884</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>20.499964</v>
+        <v>-20.499964</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>22.548709</v>
+        <v>-22.548709</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>27.868658</v>
+        <v>-27.868658</v>
       </c>
     </row>
     <row r="28">
@@ -1775,19 +1775,19 @@
         <v>-1.059681</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>5.476554</v>
+        <v>-5.476554</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>8.076884</v>
+        <v>-8.076884</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>20.499964</v>
+        <v>-20.499964</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>22.759111</v>
+        <v>-22.338307</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>28.16701</v>
+        <v>-27.570306</v>
       </c>
     </row>
     <row r="30">
@@ -1893,19 +1893,19 @@
         <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -4726,43 +4726,43 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.467423</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>21.242953</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>22.229164</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>22.254306</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>22.743237</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>23.431322</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>23.882702</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>24.064449</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>24.284402</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>24.284402</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>13.084647</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>14.095979</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>14.609347</v>
       </c>
     </row>
     <row r="93">
@@ -7993,7 +7993,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -9813,7 +9817,11 @@
           <t>Reserves 10 13,084,647 12,040,516</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -11486,7 +11494,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -13400,7 +13412,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>-</t>
@@ -15447,7 +15463,11 @@
           <t>Reserves 22,743,237</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
@@ -16188,7 +16208,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
@@ -17397,7 +17421,11 @@
           <t>Reserves (Note 5)</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>-</t>
@@ -18219,7 +18247,11 @@
           <t>Reserves (Note 5)</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E142" s="5" t="n">
         <v>1.467423</v>
       </c>
@@ -31466,19 +31498,19 @@
         </is>
       </c>
       <c r="M307" s="5" t="n">
-        <v>5.476554</v>
+        <v>-5.476554</v>
       </c>
       <c r="N307" s="5" t="n">
-        <v>8.076884</v>
+        <v>-8.076884</v>
       </c>
       <c r="O307" s="5" t="n">
-        <v>20.499964</v>
+        <v>-20.499964</v>
       </c>
       <c r="P307" s="5" t="n">
-        <v>22.548709</v>
+        <v>-22.548709</v>
       </c>
       <c r="Q307" s="5" t="n">
-        <v>27.868658</v>
+        <v>-27.868658</v>
       </c>
     </row>
     <row r="308">

--- a/output/pdf_financials_xlsx/FDY.xlsx
+++ b/output/pdf_financials_xlsx/FDY.xlsx
@@ -936,16 +936,16 @@
         <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.202565</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.863214</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-1.324215</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.914231</v>
       </c>
     </row>
     <row r="13">
@@ -1686,16 +1686,16 @@
         <v>-5.476554</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-8.076884</v>
+        <v>-8.279449</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-20.499964</v>
+        <v>-19.63675</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-22.548709</v>
+        <v>-21.224494</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-27.868658</v>
+        <v>-26.954427</v>
       </c>
     </row>
     <row r="28">
@@ -1778,16 +1778,16 @@
         <v>-5.476554</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-8.076884</v>
+        <v>-8.279449</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-20.499964</v>
+        <v>-19.63675</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-22.338307</v>
+        <v>-21.014092</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-27.570306</v>
+        <v>-26.656075</v>
       </c>
     </row>
     <row r="30">
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.048271</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.772418</v>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.048271</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.772418</v>
@@ -2638,7 +2638,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.057187</v>
+        <v>0.008916</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.052774</v>
@@ -12065,7 +12065,11 @@
           <t>Reclamation deposit 5</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
@@ -13898,7 +13902,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -14961,7 +14969,11 @@
           <t>Reclamation deposit 5 2,509</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
@@ -16775,7 +16787,11 @@
           <t>Reclamation deposit (Note 6)</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E124" s="5" t="n">
         <v>0.037943</v>
       </c>
@@ -17834,7 +17850,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E137" s="5" t="n">
@@ -29696,7 +29712,11 @@
           <t>Refund of reclamation deposit</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr"/>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E285" s="5" t="n">
         <v>0.15058</v>
       </c>
@@ -31290,7 +31310,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -35749,7 +35769,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">

--- a/output/pdf_financials_xlsx/FDY.xlsx
+++ b/output/pdf_financials_xlsx/FDY.xlsx
@@ -5613,13 +5613,13 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>0.054597</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.279152</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.014709</v>
       </c>
       <c r="E112" s="3" t="n">
         <v>0</v>
@@ -5631,7 +5631,7 @@
         <v>0</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.008859000000000001</v>
       </c>
       <c r="I112" s="3" t="n">
         <v>0</v>
@@ -25917,7 +25917,11 @@
           <t>Proceeds from disposition of property and equipment</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr"/>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr">
         <is>
           <t>-</t>
@@ -29635,7 +29639,11 @@
           <t>Proceeds from sale of property and equipment</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E284" s="5" t="n">
         <v>0.054597</v>
       </c>

--- a/output/pdf_financials_xlsx/FDY.xlsx
+++ b/output/pdf_financials_xlsx/FDY.xlsx
@@ -5631,7 +5631,7 @@
         <v>0</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0.008859000000000001</v>
+        <v>0</v>
       </c>
       <c r="I112" s="3" t="n">
         <v>0</v>
@@ -19503,7 +19503,11 @@
           <t>Proceeds from issuance of common shares in private placement</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
           <t>-</t>
@@ -23926,7 +23930,11 @@
           <t>Shares issued for private placement</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E213" t="inlineStr">
         <is>
           <t>-</t>
@@ -25690,7 +25698,11 @@
           <t>Shares issuance for cash</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr">
         <is>
           <t>-</t>
@@ -25917,11 +25929,7 @@
           <t>Proceeds from disposition of property and equipment</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>SaleOfPPE</t>
-        </is>
-      </c>
+      <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr">
         <is>
           <t>-</t>
